--- a/.claude/skills/wagebook-convert/templates/賃金台帳テンプレート.xlsx
+++ b/.claude/skills/wagebook-convert/templates/賃金台帳テンプレート.xlsx
@@ -508,7 +508,8 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>※金額は課税支給合計（税込）を入力してください。支給がない月は空欄のままにしてください。　／ S列「年間通勤手当」には非課税通勤手当の年間合計を入力（ツールが在籍月数で均等割して各月から自動減算します）。「課税支給合計」列がある台帳ではS列空欄でOK。</t>
+          <t>※金額は課税支給合計（税込）を入力してください。支給がない月は空欄のままにしてください。　／ S列「年間通勤手当」には非課税通勤手当の年間合計を入力（ツールが在籍月数で均等割して各月から自動減算します）。「課税支給合計」列がある台帳ではS列空欄でOK。
+E列「月間平均時間」・F列「時給」は ★パート・アルバイトでは必須★（IT導入補助金 R215 FTE換算用、公募要領 p.10）。正社員・役員は空欄可。</t>
         </is>
       </c>
     </row>
@@ -901,7 +902,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>年間の月平均労働時間（例: 160）</t>
+          <t>年間の月平均労働時間（例: 160）。★パート・アルバイトでは必須★（IT導入補助金 R215 FTE換算用）。正社員は空欄可</t>
         </is>
       </c>
     </row>
@@ -913,7 +914,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>時給換算額（月給の場合: 月給÷月間平均時間）</t>
+          <t>時給換算額（月給の場合: 月給÷月間平均時間）。★パート・アルバイトでは必須★。正社員は空欄可</t>
         </is>
       </c>
     </row>

--- a/.claude/skills/wagebook-convert/templates/賃金台帳テンプレート.xlsx
+++ b/.claude/skills/wagebook-convert/templates/賃金台帳テンプレート.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:S15"/>
+  <dimension ref="B2:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -489,6 +489,7 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -509,7 +510,7 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>※金額は課税支給合計（税込）を入力してください。支給がない月は空欄のままにしてください。　／ S列「年間通勤手当」には非課税通勤手当の年間合計を入力（ツールが在籍月数で均等割して各月から自動減算します）。「課税支給合計」列がある台帳ではS列空欄でOK。
-E列「月間平均時間」・F列「時給」は ★パート・アルバイトでは必須★（IT導入補助金 R215 FTE換算用、公募要領 p.10）。正社員・役員は空欄可。</t>
+E列「月間平均時間」・F列「時給」は ★パート・アルバイトでは必須★（IT導入補助金 R215 FTE換算用、公募要領 p.10）。正社員・役員は空欄可。／ T列「年間賞与」には課税賞与の年間合計を入力（月次セルには混ぜない。ツールが給与支給総額R216に算入。賞与の支給月は問わない）。</t>
         </is>
       </c>
     </row>
@@ -602,6 +603,11 @@
       <c r="S5" s="3" t="inlineStr">
         <is>
           <t>年間通勤手当</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>年間賞与</t>
         </is>
       </c>
     </row>
@@ -844,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -858,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -939,6 +946,18 @@
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>非課税通勤手当の年間合計（円）。月給に通勤費が混入する台帳でのみ記入。給与計算ソフトの「課税支給合計」列を直接転記している場合は空欄でOK。月割で各月の支給額から自動減算される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>年間賞与</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>課税賞与の年間合計（円）。月次（1月〜12月列）には入れない。ツールが給与支給総額に算入する。支給月は問わない。</t>
         </is>
       </c>
     </row>

--- a/.claude/skills/wagebook-convert/templates/賃金台帳テンプレート.xlsx
+++ b/.claude/skills/wagebook-convert/templates/賃金台帳テンプレート.xlsx
@@ -509,7 +509,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>※金額は課税支給合計（税込）を入力してください。支給がない月は空欄のままにしてください。　／ S列「年間通勤手当」には非課税通勤手当の年間合計を入力（ツールが在籍月数で均等割して各月から自動減算します）。「課税支給合計」列がある台帳ではS列空欄でOK。
+          <t>※金額は課税支給合計（税込）を入力してください。支給がない月は空欄のままにしてください。　／ S列「年間通勤手当」には、毎月の欄に入れた金額に含まれている通勤手当の年間合計を入力（課税・非課税を問いません。ツールが在籍月数で均等割して各月から自動減算します）。毎月の欄が「課税支給合計」で通勤手当がそこに含まれていない場合は空欄。
 E列「月間平均時間」・F列「時給」は ★パート・アルバイトでは必須★（IT導入補助金 R215 FTE換算用、公募要領 p.10）。正社員・役員は空欄可。／ T列「年間賞与」には課税賞与の年間合計を入力（月次セルには混ぜない。ツールが給与支給総額R216に算入。賞与の支給月は問わない）。</t>
         </is>
       </c>
@@ -864,7 +864,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -945,7 +944,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>非課税通勤手当の年間合計（円）。月給に通勤費が混入する台帳でのみ記入。給与計算ソフトの「課税支給合計」列を直接転記している場合は空欄でOK。月割で各月の支給額から自動減算される。</t>
+          <t>毎月の欄に入れた金額に含まれている通勤手当の年間合計（円）。課税・非課税を問わず控除する（2026-07-27 運用）。毎月の欄が「課税支給合計」で通勤手当がそこに含まれていない（非課税処理されている）場合は空欄。月割で各月の支給額から自動減算される。</t>
         </is>
       </c>
     </row>
